--- a/data/xlsx/sbce_config_kvm_ems_emssec_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_emssec_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EMS1" sheetId="1" state="visible" r:id="rId3"/>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
